--- a/registration_forms/048_press_interview_slot_registration--registration_forms.xlsx
+++ b/registration_forms/048_press_interview_slot_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Journalist Details Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Journalist Details Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Journalist Details Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'journalist'}</t>
+          <t>journalist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Journalist'}</t>
+          <t>Journalist</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'media_professional'}</t>
+          <t>media_professional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Media Professional'}</t>
+          <t>Media Professional</t>
         </is>
       </c>
     </row>
